--- a/drg/for analysis/results/Load Calculation Sheet.xlsx
+++ b/drg/for analysis/results/Load Calculation Sheet.xlsx
@@ -3936,13 +3936,13 @@
       </c>
       <c r="C44" s="53">
         <f>ROUNDUP(((G44*12)+H44)*0.0254,3)</f>
-        <v>1.5499999999999998</v>
+        <v>3.5059999999999998</v>
       </c>
       <c r="G44" s="29">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H44" s="30">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="C45" s="53">
         <f>ROUNDUP(((G45*12)+H45)*0.0254,3)</f>
-        <v>1.956</v>
+        <v>4.0900000000000007</v>
       </c>
       <c r="D45" s="54"/>
       <c r="E45" s="54"/>
       <c r="G45" s="29">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H45" s="55">
         <v>5</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C46" s="93" t="str">
         <f>CONCATENATE(C44,"*",C45)</f>
-        <v>1.55*1.956</v>
+        <v>3.506*4.09</v>
       </c>
       <c r="D46" s="54"/>
       <c r="E46" s="54"/>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C47" s="16">
         <f>C44*C45</f>
-        <v>3.0317999999999996</v>
+        <v>14.339540000000001</v>
       </c>
       <c r="D47" s="54"/>
       <c r="E47" s="58"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C50" s="38" t="str">
         <f>CONCATENATE((C48/100),"/",ROUND(C47,3))</f>
-        <v>20/3.032</v>
+        <v>20/14.34</v>
       </c>
       <c r="D50" s="32"/>
       <c r="E50" s="32"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C51" s="62">
         <f>(C48/100)/C47</f>
-        <v>6.5967412098423388</v>
+        <v>1.3947448802402307</v>
       </c>
       <c r="D51" s="32"/>
       <c r="E51" s="32"/>
